--- a/financials/PNJ/PNJ.xlsx
+++ b/financials/PNJ/PNJ.xlsx
@@ -22,10 +22,10 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0 &quot;ngày&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,44 +47,52 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <b val="1"/>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
+      <charset val="1"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
+      <charset val="1"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <color rgb="00000000"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Tahoma"/>
-      <color rgb="00008000"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -102,11 +110,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -134,11 +143,41 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -148,24 +187,57 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -6531,1711 +6603,2822 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="38.33203125" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>CHỈ SỐ TÀI CHÍNH — PNJ</t>
-        </is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B1" s="6">
+        <f>balance_sheet!B1</f>
+        <v/>
+      </c>
+      <c r="C1" s="6">
+        <f>balance_sheet!C1</f>
+        <v/>
+      </c>
+      <c r="D1" s="6">
+        <f>balance_sheet!D1</f>
+        <v/>
+      </c>
+      <c r="E1" s="6">
+        <f>balance_sheet!E1</f>
+        <v/>
+      </c>
+      <c r="F1" s="6">
+        <f>balance_sheet!F1</f>
+        <v/>
+      </c>
+      <c r="G1" s="6">
+        <f>balance_sheet!G1</f>
+        <v/>
+      </c>
+      <c r="H1" s="6">
+        <f>balance_sheet!H1</f>
+        <v/>
+      </c>
+      <c r="I1" s="6">
+        <f>balance_sheet!I1</f>
+        <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>I. CHỈ SỐ TÀI CHÍNH</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C2" s="8">
+        <f>IFERROR(C$39/((C$24+B$24)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D2" s="8">
+        <f>IFERROR(D$39/((D$24+C$24)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E2" s="8">
+        <f>IFERROR(E$39/((E$24+D$24)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F2" s="8">
+        <f>IFERROR(F$39/((F$24+E$24)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G2" s="8">
+        <f>IFERROR(G$39/((G$24+F$24)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H2" s="8">
+        <f>IFERROR(H$39/((H$24+G$24)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I2" s="8">
+        <f>IFERROR(I$39/((I$24+H$24)/2),"n/a")</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Chỉ tiêu</t>
-        </is>
-      </c>
-      <c r="B3" s="9">
-        <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C3" s="9">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D3" s="9">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E3" s="9">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="F3" s="9">
-        <f>'balance_sheet'!F1</f>
-        <v/>
-      </c>
-      <c r="G3" s="9">
-        <f>'balance_sheet'!G1</f>
-        <v/>
-      </c>
-      <c r="H3" s="9">
-        <f>'balance_sheet'!H1</f>
-        <v/>
-      </c>
-      <c r="I3" s="9">
-        <f>'balance_sheet'!I1</f>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ROA (LNST / Tổng tài sản bình quân)</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C3" s="8">
+        <f>IFERROR(C$38/((C$25+B$25)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D3" s="8">
+        <f>IFERROR(D$38/((D$25+C$25)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E3" s="8">
+        <f>IFERROR(E$38/((E$25+D$25)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F3" s="8">
+        <f>IFERROR(F$38/((F$25+E$25)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G3" s="8">
+        <f>IFERROR(G$38/((G$25+F$25)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H3" s="8">
+        <f>IFERROR(H$38/((H$25+G$25)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I3" s="8">
+        <f>IFERROR(I$38/((I$25+H$25)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>1. Khả năng sinh lời</t>
-        </is>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C4" s="8">
+        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D4" s="8">
+        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E4" s="8">
+        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F4" s="8">
+        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G4" s="8">
+        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H4" s="8">
+        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I4" s="8">
+        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Tăng trưởng Doanh thu thuần</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C5" s="13">
-        <f>IFERROR(C$47/((C$32+B$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D5" s="13">
-        <f>IFERROR(D$47/((D$32+C$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E5" s="13">
-        <f>IFERROR(E$47/((E$32+D$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>IFERROR(F$47/((F$32+E$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>IFERROR(G$47/((G$32+F$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H5" s="13">
-        <f>IFERROR(H$47/((H$32+G$32)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I5" s="13">
-        <f>IFERROR(I$47/((I$32+H$32)/2),"n/a")</f>
+      <c r="C5" s="8">
+        <f>IFERROR((C$31-B$31)/ABS(B$31),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D5" s="8">
+        <f>IFERROR((D$31-C$31)/ABS(C$31),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E5" s="8">
+        <f>IFERROR((E$31-D$31)/ABS(D$31),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F5" s="8">
+        <f>IFERROR((F$31-E$31)/ABS(E$31),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G5" s="8">
+        <f>IFERROR((G$31-F$31)/ABS(F$31),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H5" s="8">
+        <f>IFERROR((H$31-G$31)/ABS(G$31),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I5" s="8">
+        <f>IFERROR((I$31-H$31)/ABS(H$31),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>ROA (LNST / Tổng tài sản bình quân)</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C6" s="13">
-        <f>IFERROR(C$46/((C$33+B$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D6" s="13">
-        <f>IFERROR(D$46/((D$33+C$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E6" s="13">
-        <f>IFERROR(E$46/((E$33+D$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F6" s="13">
-        <f>IFERROR(F$46/((F$33+E$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>IFERROR(G$46/((G$33+F$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H6" s="13">
-        <f>IFERROR(H$46/((H$33+G$33)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I6" s="13">
-        <f>IFERROR(I$46/((I$33+H$33)/2),"n/a")</f>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận gộp</t>
+        </is>
+      </c>
+      <c r="B6" s="8">
+        <f>IFERROR(B$33/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C6" s="8">
+        <f>IFERROR(C$33/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D6" s="8">
+        <f>IFERROR(D$33/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>IFERROR(E$33/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F6" s="8">
+        <f>IFERROR(F$33/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G6" s="8">
+        <f>IFERROR(G$33/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H6" s="8">
+        <f>IFERROR(H$33/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I6" s="8">
+        <f>IFERROR(I$33/I$31,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C7" s="13">
-        <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D7" s="13">
-        <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>IFERROR((F$47-E$47)/ABS(E$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G7" s="13">
-        <f>IFERROR((G$47-F$47)/ABS(F$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H7" s="13">
-        <f>IFERROR((H$47-G$47)/ABS(G$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I7" s="13">
-        <f>IFERROR((I$47-H$47)/ABS(H$47),"n/a")</f>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận ròng</t>
+        </is>
+      </c>
+      <c r="B7" s="8">
+        <f>IFERROR(B$38/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C7" s="8">
+        <f>IFERROR(C$38/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D7" s="8">
+        <f>IFERROR(D$38/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>IFERROR(E$38/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F7" s="8">
+        <f>IFERROR(F$38/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G7" s="8">
+        <f>IFERROR(G$38/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H7" s="8">
+        <f>IFERROR(H$38/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I7" s="8">
+        <f>IFERROR(I$38/I$31,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Tăng trưởng Doanh thu thuần</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C8" s="13">
-        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D8" s="13">
-        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E8" s="13">
-        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F8" s="13">
-        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G8" s="13">
-        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H8" s="13">
-        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I8" s="13">
-        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
+        </is>
+      </c>
+      <c r="B8" s="9">
+        <f>IFERROR((B$29+B$30)/B$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C8" s="9">
+        <f>IFERROR((C$29+C$30)/C$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D8" s="9">
+        <f>IFERROR((D$29+D$30)/D$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E8" s="9">
+        <f>IFERROR((E$29+E$30)/E$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F8" s="9">
+        <f>IFERROR((F$29+F$30)/F$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G8" s="9">
+        <f>IFERROR((G$29+G$30)/G$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H8" s="9">
+        <f>IFERROR((H$29+H$30)/H$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I8" s="9">
+        <f>IFERROR((I$29+I$30)/I$24,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2. Biên lợi nhuận</t>
-        </is>
+          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B9" s="9">
+        <f>IFERROR(B$30/B$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C9" s="9">
+        <f>IFERROR(C$30/C$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D9" s="9">
+        <f>IFERROR(D$30/D$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E9" s="9">
+        <f>IFERROR(E$30/E$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F9" s="9">
+        <f>IFERROR(F$30/F$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
+        <f>IFERROR(G$30/G$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>IFERROR(H$30/H$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I9" s="9">
+        <f>IFERROR(I$30/I$24,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận gộp</t>
-        </is>
-      </c>
-      <c r="B10" s="13">
-        <f>IFERROR(B$41/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C10" s="13">
-        <f>IFERROR(C$41/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D10" s="13">
-        <f>IFERROR(D$41/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E10" s="13">
-        <f>IFERROR(E$41/E$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F10" s="13">
-        <f>IFERROR(F$41/F$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G10" s="13">
-        <f>IFERROR(G$41/G$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H10" s="13">
-        <f>IFERROR(H$41/H$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I10" s="13">
-        <f>IFERROR(I$41/I$39,"n/a")</f>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>IFERROR(B$29/B$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C10" s="9">
+        <f>IFERROR(C$29/C$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D10" s="9">
+        <f>IFERROR(D$29/D$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E10" s="9">
+        <f>IFERROR(E$29/E$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F10" s="9">
+        <f>IFERROR(F$29/F$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G10" s="9">
+        <f>IFERROR(G$29/G$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H10" s="9">
+        <f>IFERROR(H$29/H$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I10" s="9">
+        <f>IFERROR(I$29/I$24,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận ròng</t>
-        </is>
-      </c>
-      <c r="B11" s="13">
-        <f>IFERROR(B$46/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C11" s="13">
-        <f>IFERROR(C$46/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D11" s="13">
-        <f>IFERROR(D$46/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E11" s="13">
-        <f>IFERROR(E$46/E$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F11" s="13">
-        <f>IFERROR(F$46/F$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G11" s="13">
-        <f>IFERROR(G$46/G$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H11" s="13">
-        <f>IFERROR(H$46/H$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I11" s="13">
-        <f>IFERROR(I$46/I$39,"n/a")</f>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Nợ phải trả/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B11" s="9">
+        <f>IFERROR(B$26/B$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C11" s="9">
+        <f>IFERROR(C$26/C$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D11" s="9">
+        <f>IFERROR(D$26/D$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E11" s="9">
+        <f>IFERROR(E$26/E$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F11" s="9">
+        <f>IFERROR(F$26/F$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G11" s="9">
+        <f>IFERROR(G$26/G$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H11" s="9">
+        <f>IFERROR(H$26/H$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I11" s="9">
+        <f>IFERROR(I$26/I$24,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>3. Đòn bẩy tài chính</t>
-        </is>
+          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
+        <f>IFERROR(B$28/B$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C12" s="9">
+        <f>IFERROR(C$28/C$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D12" s="9">
+        <f>IFERROR(D$28/D$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E12" s="9">
+        <f>IFERROR(E$28/E$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F12" s="9">
+        <f>IFERROR(F$28/F$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>IFERROR(G$28/G$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>IFERROR(H$28/H$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I12" s="9">
+        <f>IFERROR(I$28/I$24,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
-        </is>
-      </c>
-      <c r="B13" s="14">
-        <f>IFERROR((B$37+B$38)/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C13" s="14">
-        <f>IFERROR((C$37+C$38)/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D13" s="14">
-        <f>IFERROR((D$37+D$38)/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E13" s="14">
-        <f>IFERROR((E$37+E$38)/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F13" s="14">
-        <f>IFERROR((F$37+F$38)/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
-        <f>IFERROR((G$37+G$38)/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H13" s="14">
-        <f>IFERROR((H$37+H$38)/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I13" s="14">
-        <f>IFERROR((I$37+I$38)/I$32,"n/a")</f>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>IFERROR(B$27/B$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C13" s="9">
+        <f>IFERROR(C$27/C$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D13" s="9">
+        <f>IFERROR(D$27/D$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E13" s="9">
+        <f>IFERROR(E$27/E$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F13" s="9">
+        <f>IFERROR(F$27/F$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G13" s="9">
+        <f>IFERROR(G$27/G$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H13" s="9">
+        <f>IFERROR(H$27/H$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I13" s="9">
+        <f>IFERROR(I$27/I$24,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B14" s="14">
-        <f>IFERROR(B$38/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C14" s="14">
-        <f>IFERROR(C$38/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D14" s="14">
-        <f>IFERROR(D$38/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E14" s="14">
-        <f>IFERROR(E$38/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F14" s="14">
-        <f>IFERROR(F$38/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
-        <f>IFERROR(G$38/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H14" s="14">
-        <f>IFERROR(H$38/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I14" s="14">
-        <f>IFERROR(I$38/I$32,"n/a")</f>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Chi phí bán hàng, quản lý/LN gộp</t>
+        </is>
+      </c>
+      <c r="B14" s="8">
+        <f>IFERROR((ABS(B$34)+ABS(B$35))/B$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C14" s="8">
+        <f>IFERROR((ABS(C$34)+ABS(C$35))/C$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D14" s="8">
+        <f>IFERROR((ABS(D$34)+ABS(D$35))/D$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E14" s="8">
+        <f>IFERROR((ABS(E$34)+ABS(E$35))/E$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F14" s="8">
+        <f>IFERROR((ABS(F$34)+ABS(F$35))/F$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G14" s="8">
+        <f>IFERROR((ABS(G$34)+ABS(G$35))/G$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H14" s="8">
+        <f>IFERROR((ABS(H$34)+ABS(H$35))/H$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I14" s="8">
+        <f>IFERROR((ABS(I$34)+ABS(I$35))/I$33,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B15" s="14">
-        <f>IFERROR(B$37/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C15" s="14">
-        <f>IFERROR(C$37/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D15" s="14">
-        <f>IFERROR(D$37/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E15" s="14">
-        <f>IFERROR(E$37/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F15" s="14">
-        <f>IFERROR(F$37/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G15" s="14">
-        <f>IFERROR(G$37/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H15" s="14">
-        <f>IFERROR(H$37/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I15" s="14">
-        <f>IFERROR(I$37/I$32,"n/a")</f>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B15" s="8">
+        <f>IFERROR(ABS(B$37)/B$36,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C15" s="8">
+        <f>IFERROR(ABS(C$37)/C$36,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D15" s="8">
+        <f>IFERROR(ABS(D$37)/D$36,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E15" s="8">
+        <f>IFERROR(ABS(E$37)/E$36,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F15" s="8">
+        <f>IFERROR(ABS(F$37)/F$36,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G15" s="8">
+        <f>IFERROR(ABS(G$37)/G$36,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H15" s="8">
+        <f>IFERROR(ABS(H$37)/H$36,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I15" s="8">
+        <f>IFERROR(ABS(I$37)/I$36,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Nợ phải trả/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B16" s="14">
-        <f>IFERROR(B$34/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C16" s="14">
-        <f>IFERROR(C$34/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D16" s="14">
-        <f>IFERROR(D$34/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E16" s="14">
-        <f>IFERROR(E$34/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F16" s="14">
-        <f>IFERROR(F$34/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G16" s="14">
-        <f>IFERROR(G$34/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H16" s="14">
-        <f>IFERROR(H$34/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I16" s="14">
-        <f>IFERROR(I$34/I$32,"n/a")</f>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Số ngày phải trả (DPO)</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C16" s="12">
+        <f>IFERROR(((C$41+B$41)/2)/ABS(C$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D16" s="12">
+        <f>IFERROR(((D$41+C$41)/2)/ABS(D$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E16" s="12">
+        <f>IFERROR(((E$41+D$41)/2)/ABS(E$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F16" s="12">
+        <f>IFERROR(((F$41+E$41)/2)/ABS(F$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G16" s="12">
+        <f>IFERROR(((G$41+F$41)/2)/ABS(G$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H16" s="12">
+        <f>IFERROR(((H$41+G$41)/2)/ABS(H$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I16" s="12">
+        <f>IFERROR(((I$41+H$41)/2)/ABS(I$32)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B17" s="14">
-        <f>IFERROR(B$36/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C17" s="14">
-        <f>IFERROR(C$36/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D17" s="14">
-        <f>IFERROR(D$36/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E17" s="14">
-        <f>IFERROR(E$36/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F17" s="14">
-        <f>IFERROR(F$36/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G17" s="14">
-        <f>IFERROR(G$36/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H17" s="14">
-        <f>IFERROR(H$36/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I17" s="14">
-        <f>IFERROR(I$36/I$32,"n/a")</f>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Số ngày phải thu (DSO)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C17" s="12">
+        <f>IFERROR(((C$40+B$40)/2)/C$31*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D17" s="12">
+        <f>IFERROR(((D$40+C$40)/2)/D$31*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>IFERROR(((E$40+D$40)/2)/E$31*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F17" s="12">
+        <f>IFERROR(((F$40+E$40)/2)/F$31*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G17" s="12">
+        <f>IFERROR(((G$40+F$40)/2)/G$31*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H17" s="12">
+        <f>IFERROR(((H$40+G$40)/2)/H$31*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I17" s="12">
+        <f>IFERROR(((I$40+H$40)/2)/I$31*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B18" s="14">
-        <f>IFERROR(B$35/B$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C18" s="14">
-        <f>IFERROR(C$35/C$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D18" s="14">
-        <f>IFERROR(D$35/D$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E18" s="14">
-        <f>IFERROR(E$35/E$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F18" s="14">
-        <f>IFERROR(F$35/F$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G18" s="14">
-        <f>IFERROR(G$35/G$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H18" s="14">
-        <f>IFERROR(H$35/H$32,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I18" s="14">
-        <f>IFERROR(I$35/I$32,"n/a")</f>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Số ngày tồn kho (DIO)</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C18" s="12">
+        <f>IFERROR(((C$42+B$42)/2)/ABS(C$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D18" s="12">
+        <f>IFERROR(((D$42+C$42)/2)/ABS(D$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>IFERROR(((E$42+D$42)/2)/ABS(E$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F18" s="12">
+        <f>IFERROR(((F$42+E$42)/2)/ABS(F$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G18" s="12">
+        <f>IFERROR(((G$42+F$42)/2)/ABS(G$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H18" s="12">
+        <f>IFERROR(((H$42+G$42)/2)/ABS(H$32)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I18" s="12">
+        <f>IFERROR(((I$42+H$42)/2)/ABS(I$32)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>4. Chi phí &amp; khả năng trả lãi</t>
-        </is>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền/Tài sản</t>
+        </is>
+      </c>
+      <c r="B19" s="8">
+        <f>IFERROR(B$43/B$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C19" s="8">
+        <f>IFERROR(C$43/C$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D19" s="8">
+        <f>IFERROR(D$43/D$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E19" s="8">
+        <f>IFERROR(E$43/E$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F19" s="8">
+        <f>IFERROR(F$43/F$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G19" s="8">
+        <f>IFERROR(G$43/G$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H19" s="8">
+        <f>IFERROR(H$43/H$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I19" s="8">
+        <f>IFERROR(I$43/I$25,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Chi phí bán hàng, quản lý/LN gộp</t>
-        </is>
-      </c>
-      <c r="B20" s="13">
-        <f>IFERROR((ABS(B$42)+ABS(B$43))/B$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C20" s="13">
-        <f>IFERROR((ABS(C$42)+ABS(C$43))/C$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D20" s="13">
-        <f>IFERROR((ABS(D$42)+ABS(D$43))/D$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E20" s="13">
-        <f>IFERROR((ABS(E$42)+ABS(E$43))/E$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F20" s="13">
-        <f>IFERROR((ABS(F$42)+ABS(F$43))/F$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G20" s="13">
-        <f>IFERROR((ABS(G$42)+ABS(G$43))/G$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H20" s="13">
-        <f>IFERROR((ABS(H$42)+ABS(H$43))/H$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I20" s="13">
-        <f>IFERROR((ABS(I$42)+ABS(I$43))/I$41,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
-        </is>
-      </c>
-      <c r="B21" s="13">
-        <f>IFERROR(ABS(B$45)/B$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C21" s="13">
-        <f>IFERROR(ABS(C$45)/C$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D21" s="13">
-        <f>IFERROR(ABS(D$45)/D$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E21" s="13">
-        <f>IFERROR(ABS(E$45)/E$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F21" s="13">
-        <f>IFERROR(ABS(F$45)/F$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G21" s="13">
-        <f>IFERROR(ABS(G$45)/G$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H21" s="13">
-        <f>IFERROR(ABS(H$45)/H$44,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I21" s="13">
-        <f>IFERROR(ABS(I$45)/I$44,"n/a")</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho/Tài sản</t>
+        </is>
+      </c>
+      <c r="B20" s="8">
+        <f>IFERROR(B$42/B$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C20" s="8">
+        <f>IFERROR(C$42/C$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D20" s="8">
+        <f>IFERROR(D$42/D$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E20" s="8">
+        <f>IFERROR(E$42/E$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F20" s="8">
+        <f>IFERROR(F$42/F$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G20" s="8">
+        <f>IFERROR(G$42/G$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H20" s="8">
+        <f>IFERROR(H$42/H$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I20" s="8">
+        <f>IFERROR(I$42/I$25,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>5. Chu kỳ hoạt động vốn lưu động</t>
-        </is>
-      </c>
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Số ngày phải trả (DPO)</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C23" s="15">
-        <f>IFERROR(((C$49+B$49)/2)/ABS(C$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D23" s="15">
-        <f>IFERROR(((D$49+C$49)/2)/ABS(D$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E23" s="15">
-        <f>IFERROR(((E$49+D$49)/2)/ABS(E$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F23" s="15">
-        <f>IFERROR(((F$49+E$49)/2)/ABS(F$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G23" s="15">
-        <f>IFERROR(((G$49+F$49)/2)/ABS(G$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H23" s="15">
-        <f>IFERROR(((H$49+G$49)/2)/ABS(H$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I23" s="15">
-        <f>IFERROR(((I$49+H$49)/2)/ABS(I$40)*365,"n/a")</f>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Khoản mục</t>
+        </is>
+      </c>
+      <c r="B23" s="16">
+        <f>balance_sheet!B1</f>
+        <v/>
+      </c>
+      <c r="C23" s="16">
+        <f>balance_sheet!C1</f>
+        <v/>
+      </c>
+      <c r="D23" s="16">
+        <f>balance_sheet!D1</f>
+        <v/>
+      </c>
+      <c r="E23" s="16">
+        <f>balance_sheet!E1</f>
+        <v/>
+      </c>
+      <c r="F23" s="16">
+        <f>balance_sheet!F1</f>
+        <v/>
+      </c>
+      <c r="G23" s="16">
+        <f>balance_sheet!G1</f>
+        <v/>
+      </c>
+      <c r="H23" s="16">
+        <f>balance_sheet!H1</f>
+        <v/>
+      </c>
+      <c r="I23" s="16">
+        <f>balance_sheet!I1</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Số ngày phải thu (DSO)</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C24" s="15">
-        <f>IFERROR(((C$48+B$48)/2)/C$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D24" s="15">
-        <f>IFERROR(((D$48+C$48)/2)/D$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E24" s="15">
-        <f>IFERROR(((E$48+D$48)/2)/E$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F24" s="15">
-        <f>IFERROR(((F$48+E$48)/2)/F$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G24" s="15">
-        <f>IFERROR(((G$48+F$48)/2)/G$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H24" s="15">
-        <f>IFERROR(((H$48+G$48)/2)/H$39*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I24" s="15">
-        <f>IFERROR(((I$48+H$48)/2)/I$39*365,"n/a")</f>
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B24" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Số ngày tồn kho (DIO)</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C25" s="15">
-        <f>IFERROR(((C$50+B$50)/2)/ABS(C$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D25" s="15">
-        <f>IFERROR(((D$50+C$50)/2)/ABS(D$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E25" s="15">
-        <f>IFERROR(((E$50+D$50)/2)/ABS(E$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F25" s="15">
-        <f>IFERROR(((F$50+E$50)/2)/ABS(F$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G25" s="15">
-        <f>IFERROR(((G$50+F$50)/2)/ABS(G$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H25" s="15">
-        <f>IFERROR(((H$50+G$50)/2)/ABS(H$40)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I25" s="15">
-        <f>IFERROR(((I$50+H$50)/2)/ABS(I$40)*365,"n/a")</f>
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG TÀI SẢN</t>
+        </is>
+      </c>
+      <c r="B25" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>6. Cơ cấu tài sản</t>
-        </is>
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>NỢ PHẢI TRẢ</t>
+        </is>
+      </c>
+      <c r="B26" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền/Tài sản</t>
-        </is>
-      </c>
-      <c r="B27" s="13">
-        <f>IFERROR(B$51/B$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C27" s="13">
-        <f>IFERROR(C$51/C$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D27" s="13">
-        <f>IFERROR(D$51/D$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E27" s="13">
-        <f>IFERROR(E$51/E$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F27" s="13">
-        <f>IFERROR(F$51/F$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G27" s="13">
-        <f>IFERROR(G$51/G$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H27" s="13">
-        <f>IFERROR(H$51/H$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I27" s="13">
-        <f>IFERROR(I$51/I$33,"n/a")</f>
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Nợ ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B27" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho/Tài sản</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <f>IFERROR(B$50/B$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C28" s="13">
-        <f>IFERROR(C$50/C$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D28" s="13">
-        <f>IFERROR(D$50/D$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E28" s="13">
-        <f>IFERROR(E$50/E$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F28" s="13">
-        <f>IFERROR(F$50/F$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G28" s="13">
-        <f>IFERROR(G$50/G$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H28" s="13">
-        <f>IFERROR(H$50/H$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I28" s="13">
-        <f>IFERROR(I$50/I$33,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29"/>
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Nợ dài hạn</t>
+        </is>
+      </c>
+      <c r="B28" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Vay ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B29" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Vay dài hạn</t>
+        </is>
+      </c>
+      <c r="B30" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Khoản mục</t>
-        </is>
-      </c>
-      <c r="B31" s="9">
-        <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C31" s="9">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D31" s="9">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E31" s="9">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="F31" s="9">
-        <f>'balance_sheet'!F1</f>
-        <v/>
-      </c>
-      <c r="G31" s="9">
-        <f>'balance_sheet'!G1</f>
-        <v/>
-      </c>
-      <c r="H31" s="9">
-        <f>'balance_sheet'!H1</f>
-        <v/>
-      </c>
-      <c r="I31" s="9">
-        <f>'balance_sheet'!I1</f>
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Doanh thu thuần</t>
+        </is>
+      </c>
+      <c r="B31" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>Giá vốn hàng bán</t>
+        </is>
+      </c>
+      <c r="B32" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>TỔNG CỘNG TÀI SẢN</t>
-        </is>
-      </c>
-      <c r="B33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>Lợi nhuận gộp</t>
+        </is>
+      </c>
+      <c r="B33" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>NỢ PHẢI TRẢ</t>
-        </is>
-      </c>
-      <c r="B34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>Chi phí bán hàng</t>
+        </is>
+      </c>
+      <c r="B34" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Nợ ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Chi phí quản lý doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="B35" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Nợ dài hạn</t>
-        </is>
-      </c>
-      <c r="B36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B36" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Vay ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>Chi phí lãi vay</t>
+        </is>
+      </c>
+      <c r="B37" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Vay dài hạn</t>
-        </is>
-      </c>
-      <c r="B38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>Lãi/(lỗ) thuần sau thuế</t>
+        </is>
+      </c>
+      <c r="B38" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Doanh thu thuần</t>
-        </is>
-      </c>
-      <c r="B39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
+        </is>
+      </c>
+      <c r="B39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Giá vốn hàng bán</t>
-        </is>
-      </c>
-      <c r="B40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>Phải thu khách hàng</t>
+        </is>
+      </c>
+      <c r="B40" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Lợi nhuận gộp</t>
-        </is>
-      </c>
-      <c r="B41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>Phải trả người bán</t>
+        </is>
+      </c>
+      <c r="B41" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Chi phí bán hàng</t>
-        </is>
-      </c>
-      <c r="B42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho, ròng</t>
+        </is>
+      </c>
+      <c r="B42" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Chi phí quản lý doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="B43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền</t>
+        </is>
+      </c>
+      <c r="B43" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
-        </is>
-      </c>
-      <c r="B44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>TÀI SẢN NGẮN HẠN</t>
+        </is>
+      </c>
+      <c r="B44" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Chi phí lãi vay</t>
-        </is>
-      </c>
-      <c r="B45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>GTCL tài sản cố định vô hình</t>
+        </is>
+      </c>
+      <c r="B45" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Lãi/(lỗ) thuần sau thuế</t>
-        </is>
-      </c>
-      <c r="B46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>Khấu hao TSCĐ và BĐSĐT</t>
+        </is>
+      </c>
+      <c r="B46" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
-        </is>
-      </c>
-      <c r="B47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="16">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác</t>
+        </is>
+      </c>
+      <c r="B47" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Phải thu khách hàng</t>
-        </is>
-      </c>
-      <c r="B48" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C48" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Phải trả người bán</t>
-        </is>
-      </c>
-      <c r="B49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, ròng</t>
-        </is>
-      </c>
-      <c r="B50" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C50" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D50" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E50" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G50" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền</t>
-        </is>
-      </c>
-      <c r="B51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="16">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh</t>
+        </is>
+      </c>
+      <c r="B48" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="18">
+        <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>CHỈ SỐ THÊM</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>Khả năng sinh lời &amp; hiệu quả sử dụng vốn</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="20" t="n"/>
+      <c r="E53" s="20" t="n"/>
+      <c r="F53" s="20" t="n"/>
+      <c r="G53" s="20" t="n"/>
+      <c r="H53" s="20" t="n"/>
+      <c r="I53" s="20" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>ROCE</t>
+        </is>
+      </c>
+      <c r="B54" s="21">
+        <f>IFERROR(B$56/(B$25-B$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C54" s="21">
+        <f>IFERROR(C$56/(C$25-C$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D54" s="21">
+        <f>IFERROR(D$56/(D$25-D$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E54" s="21">
+        <f>IFERROR(E$56/(E$25-E$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F54" s="21">
+        <f>IFERROR(F$56/(F$25-F$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G54" s="21">
+        <f>IFERROR(G$56/(G$25-G$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H54" s="21">
+        <f>IFERROR(H$56/(H$25-H$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I54" s="21">
+        <f>IFERROR(I$56/(I$25-I$27),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>CROIC</t>
+        </is>
+      </c>
+      <c r="B55" s="21">
+        <f>IFERROR(B$60/(B$25-B$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C55" s="21">
+        <f>IFERROR(C$60/(C$25-C$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D55" s="21">
+        <f>IFERROR(D$60/(D$25-D$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E55" s="21">
+        <f>IFERROR(E$60/(E$25-E$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F55" s="21">
+        <f>IFERROR(F$60/(F$25-F$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G55" s="21">
+        <f>IFERROR(G$60/(G$25-G$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H55" s="21">
+        <f>IFERROR(H$60/(H$25-H$27),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I55" s="21">
+        <f>IFERROR(I$60/(I$25-I$27),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B56" s="22">
+        <f>IFERROR(B$36+ABS(B$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C56" s="22">
+        <f>IFERROR(C$36+ABS(C$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D56" s="22">
+        <f>IFERROR(D$36+ABS(D$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E56" s="22">
+        <f>IFERROR(E$36+ABS(E$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F56" s="22">
+        <f>IFERROR(F$36+ABS(F$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G56" s="22">
+        <f>IFERROR(G$36+ABS(G$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H56" s="22">
+        <f>IFERROR(H$36+ABS(H$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I56" s="22">
+        <f>IFERROR(I$36+ABS(I$37),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>EBIT/DT</t>
+        </is>
+      </c>
+      <c r="B57" s="21">
+        <f>IFERROR(B$56/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C57" s="21">
+        <f>IFERROR(C$56/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D57" s="21">
+        <f>IFERROR(D$56/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E57" s="21">
+        <f>IFERROR(E$56/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F57" s="21">
+        <f>IFERROR(F$56/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G57" s="21">
+        <f>IFERROR(G$56/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H57" s="21">
+        <f>IFERROR(H$56/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I57" s="21">
+        <f>IFERROR(I$56/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>DT/TS</t>
+        </is>
+      </c>
+      <c r="B58" s="21">
+        <f>IFERROR(B$31/B$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C58" s="21">
+        <f>IFERROR(C$31/C$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D58" s="21">
+        <f>IFERROR(D$31/D$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E58" s="21">
+        <f>IFERROR(E$31/E$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F58" s="21">
+        <f>IFERROR(F$31/F$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G58" s="21">
+        <f>IFERROR(G$31/G$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H58" s="21">
+        <f>IFERROR(H$31/H$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I58" s="21">
+        <f>IFERROR(I$31/I$25,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>Dòng tiền &amp; tái đầu tư</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="n"/>
+      <c r="C59" s="20" t="n"/>
+      <c r="D59" s="20" t="n"/>
+      <c r="E59" s="20" t="n"/>
+      <c r="F59" s="20" t="n"/>
+      <c r="G59" s="20" t="n"/>
+      <c r="H59" s="20" t="n"/>
+      <c r="I59" s="20" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>FCF</t>
+        </is>
+      </c>
+      <c r="B60" s="22">
+        <f>IFERROR(B$48-ABS(B$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C60" s="22">
+        <f>IFERROR(C$48-ABS(C$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D60" s="22">
+        <f>IFERROR(D$48-ABS(D$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E60" s="22">
+        <f>IFERROR(E$48-ABS(E$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F60" s="22">
+        <f>IFERROR(F$48-ABS(F$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G60" s="22">
+        <f>IFERROR(G$48-ABS(G$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H60" s="22">
+        <f>IFERROR(H$48-ABS(H$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I60" s="22">
+        <f>IFERROR(I$48-ABS(I$47),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>FCF/DT</t>
+        </is>
+      </c>
+      <c r="B61" s="21">
+        <f>IFERROR(B$60/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C61" s="21">
+        <f>IFERROR(C$60/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D61" s="21">
+        <f>IFERROR(D$60/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E61" s="21">
+        <f>IFERROR(E$60/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F61" s="21">
+        <f>IFERROR(F$60/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G61" s="21">
+        <f>IFERROR(G$60/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H61" s="21">
+        <f>IFERROR(H$60/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I61" s="21">
+        <f>IFERROR(I$60/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>FCF/Nợ ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B62" s="21">
+        <f>IFERROR(B$60/B$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C62" s="21">
+        <f>IFERROR(C$60/C$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D62" s="21">
+        <f>IFERROR(D$60/D$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E62" s="21">
+        <f>IFERROR(E$60/E$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F62" s="21">
+        <f>IFERROR(F$60/F$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G62" s="21">
+        <f>IFERROR(G$60/G$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H62" s="21">
+        <f>IFERROR(H$60/H$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I62" s="21">
+        <f>IFERROR(I$60/I$27,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B63" s="22">
+        <f>IFERROR(ABS(B$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C63" s="22">
+        <f>IFERROR(ABS(C$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D63" s="22">
+        <f>IFERROR(ABS(D$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E63" s="22">
+        <f>IFERROR(ABS(E$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F63" s="22">
+        <f>IFERROR(ABS(F$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G63" s="22">
+        <f>IFERROR(ABS(G$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H63" s="22">
+        <f>IFERROR(ABS(H$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I63" s="22">
+        <f>IFERROR(ABS(I$47),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>Capex/TS</t>
+        </is>
+      </c>
+      <c r="B64" s="21">
+        <f>IFERROR(B$63/B$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C64" s="21">
+        <f>IFERROR(C$63/C$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D64" s="21">
+        <f>IFERROR(D$63/D$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E64" s="21">
+        <f>IFERROR(E$63/E$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F64" s="21">
+        <f>IFERROR(F$63/F$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G64" s="21">
+        <f>IFERROR(G$63/G$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H64" s="21">
+        <f>IFERROR(H$63/H$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I64" s="21">
+        <f>IFERROR(I$63/I$25,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="inlineStr">
+        <is>
+          <t>Capex/LNST</t>
+        </is>
+      </c>
+      <c r="B65" s="21">
+        <f>IFERROR(B$63/ABS(B$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C65" s="21">
+        <f>IFERROR(C$63/ABS(C$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D65" s="21">
+        <f>IFERROR(D$63/ABS(D$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E65" s="21">
+        <f>IFERROR(E$63/ABS(E$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F65" s="21">
+        <f>IFERROR(F$63/ABS(F$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G65" s="21">
+        <f>IFERROR(G$63/ABS(G$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H65" s="21">
+        <f>IFERROR(H$63/ABS(H$38),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I65" s="21">
+        <f>IFERROR(I$63/ABS(I$38),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>Chi phí khấu hao/Lợi nhuận gộp</t>
+        </is>
+      </c>
+      <c r="B66" s="21">
+        <f>IFERROR(ABS(B$46)/B$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C66" s="21">
+        <f>IFERROR(ABS(C$46)/C$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D66" s="21">
+        <f>IFERROR(ABS(D$46)/D$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E66" s="21">
+        <f>IFERROR(ABS(E$46)/E$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F66" s="21">
+        <f>IFERROR(ABS(F$46)/F$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G66" s="21">
+        <f>IFERROR(ABS(G$46)/G$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H66" s="21">
+        <f>IFERROR(ABS(H$46)/H$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I66" s="21">
+        <f>IFERROR(ABS(I$46)/I$33,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
+          <t>EBIT/Chi phí lãi vay</t>
+        </is>
+      </c>
+      <c r="B67" s="23">
+        <f>IFERROR(B$56/ABS(B$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C67" s="23">
+        <f>IFERROR(C$56/ABS(C$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D67" s="23">
+        <f>IFERROR(D$56/ABS(D$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E67" s="23">
+        <f>IFERROR(E$56/ABS(E$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F67" s="23">
+        <f>IFERROR(F$56/ABS(F$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G67" s="23">
+        <f>IFERROR(G$56/ABS(G$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H67" s="23">
+        <f>IFERROR(H$56/ABS(H$37),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I67" s="23">
+        <f>IFERROR(I$56/ABS(I$37),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="19" t="inlineStr">
+        <is>
+          <t>Vốn lưu động &amp; hiệu quả hoạt động</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="20" t="n"/>
+      <c r="E68" s="20" t="n"/>
+      <c r="F68" s="20" t="n"/>
+      <c r="G68" s="20" t="n"/>
+      <c r="H68" s="20" t="n"/>
+      <c r="I68" s="20" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>Vòng quay tiền mặt</t>
+        </is>
+      </c>
+      <c r="B69" s="24">
+        <f>IFERROR(B$17+B$18-B$16,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C69" s="24">
+        <f>IFERROR(C$17+C$18-C$16,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D69" s="24">
+        <f>IFERROR(D$17+D$18-D$16,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E69" s="24">
+        <f>IFERROR(E$17+E$18-E$16,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F69" s="24">
+        <f>IFERROR(F$17+F$18-F$16,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G69" s="24">
+        <f>IFERROR(G$17+G$18-G$16,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H69" s="24">
+        <f>IFERROR(H$17+H$18-H$16,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I69" s="24">
+        <f>IFERROR(I$17+I$18-I$16,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20" t="inlineStr">
+        <is>
+          <t>HTK/DT</t>
+        </is>
+      </c>
+      <c r="B70" s="21">
+        <f>IFERROR(B$42/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C70" s="21">
+        <f>IFERROR(C$42/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D70" s="21">
+        <f>IFERROR(D$42/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E70" s="21">
+        <f>IFERROR(E$42/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F70" s="21">
+        <f>IFERROR(F$42/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G70" s="21">
+        <f>IFERROR(G$42/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H70" s="21">
+        <f>IFERROR(H$42/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I70" s="21">
+        <f>IFERROR(I$42/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>HTK/TS</t>
+        </is>
+      </c>
+      <c r="B71" s="21">
+        <f>IFERROR(B$42/B$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C71" s="21">
+        <f>IFERROR(C$42/C$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D71" s="21">
+        <f>IFERROR(D$42/D$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E71" s="21">
+        <f>IFERROR(E$42/E$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F71" s="21">
+        <f>IFERROR(F$42/F$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G71" s="21">
+        <f>IFERROR(G$42/G$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H71" s="21">
+        <f>IFERROR(H$42/H$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I71" s="21">
+        <f>IFERROR(I$42/I$25,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>DT/TS</t>
+        </is>
+      </c>
+      <c r="B72" s="21">
+        <f>IFERROR(B$31/B$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C72" s="21">
+        <f>IFERROR(C$31/C$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D72" s="21">
+        <f>IFERROR(D$31/D$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E72" s="21">
+        <f>IFERROR(E$31/E$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F72" s="21">
+        <f>IFERROR(F$31/F$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G72" s="21">
+        <f>IFERROR(G$31/G$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H72" s="21">
+        <f>IFERROR(H$31/H$25,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I72" s="21">
+        <f>IFERROR(I$31/I$25,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>Khả năng thanh toán</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="n"/>
+      <c r="C73" s="20" t="n"/>
+      <c r="D73" s="20" t="n"/>
+      <c r="E73" s="20" t="n"/>
+      <c r="F73" s="20" t="n"/>
+      <c r="G73" s="20" t="n"/>
+      <c r="H73" s="20" t="n"/>
+      <c r="I73" s="20" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>(TS ngắn hạn − HTK)/Nợ ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B74" s="23">
+        <f>IFERROR((B$44-B$42)/B$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C74" s="23">
+        <f>IFERROR((C$44-C$42)/C$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D74" s="23">
+        <f>IFERROR((D$44-D$42)/D$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E74" s="23">
+        <f>IFERROR((E$44-E$42)/E$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F74" s="23">
+        <f>IFERROR((F$44-F$42)/F$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G74" s="23">
+        <f>IFERROR((G$44-G$42)/G$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H74" s="23">
+        <f>IFERROR((H$44-H$42)/H$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I74" s="23">
+        <f>IFERROR((I$44-I$42)/I$27,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="20" t="inlineStr">
+        <is>
+          <t>TS ngắn hạn/Nợ ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B75" s="23">
+        <f>IFERROR(B$44/B$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C75" s="23">
+        <f>IFERROR(C$44/C$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D75" s="23">
+        <f>IFERROR(D$44/D$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E75" s="23">
+        <f>IFERROR(E$44/E$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F75" s="23">
+        <f>IFERROR(F$44/F$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G75" s="23">
+        <f>IFERROR(G$44/G$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H75" s="23">
+        <f>IFERROR(H$44/H$27,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I75" s="23">
+        <f>IFERROR(I$44/I$27,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>Tài sản &amp; cơ cấu tài sản</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="n"/>
+      <c r="C76" s="20" t="n"/>
+      <c r="D76" s="20" t="n"/>
+      <c r="E76" s="20" t="n"/>
+      <c r="F76" s="20" t="n"/>
+      <c r="G76" s="20" t="n"/>
+      <c r="H76" s="20" t="n"/>
+      <c r="I76" s="20" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="20" t="inlineStr">
+        <is>
+          <t>TSCĐ vô hình</t>
+        </is>
+      </c>
+      <c r="B77" s="22">
+        <f>IFERROR(B$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C77" s="22">
+        <f>IFERROR(C$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D77" s="22">
+        <f>IFERROR(D$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E77" s="22">
+        <f>IFERROR(E$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F77" s="22">
+        <f>IFERROR(F$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G77" s="22">
+        <f>IFERROR(G$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H77" s="22">
+        <f>IFERROR(H$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I77" s="22">
+        <f>IFERROR(I$45,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>Tài sản vô hình/Giá trị sổ sách</t>
+        </is>
+      </c>
+      <c r="B78" s="21">
+        <f>IFERROR(B$45/B$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C78" s="21">
+        <f>IFERROR(C$45/C$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D78" s="21">
+        <f>IFERROR(D$45/D$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E78" s="21">
+        <f>IFERROR(E$45/E$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F78" s="21">
+        <f>IFERROR(F$45/F$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G78" s="21">
+        <f>IFERROR(G$45/G$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H78" s="21">
+        <f>IFERROR(H$45/H$24,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I78" s="21">
+        <f>IFERROR(I$45/I$24,"n/a")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
+  <conditionalFormatting sqref="B2:I2">
+    <cfRule type="cellIs" priority="14" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="1">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:I5">
+    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="1">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="between" dxfId="2">
+      <formula>0.1</formula>
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:I6">
+    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="lessThanOrEqual" dxfId="1">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="between" dxfId="2">
+      <formula>0.1</formula>
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:I7">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:I8 B11:I11">
+    <cfRule type="cellIs" priority="6" operator="lessThanOrEqual" dxfId="0">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14:I14">
+    <cfRule type="cellIs" priority="4" operator="lessThanOrEqual" dxfId="0">
+      <formula>0.3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0.7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:I19">
+    <cfRule type="cellIs" priority="2" operator="notBetween" dxfId="1">
+      <formula>0.02</formula>
+      <formula>0.3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="between" dxfId="0">
+      <formula>0.02</formula>
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>